--- a/Capacitacion 2026/Datos/participantesNORTE.xlsx
+++ b/Capacitacion 2026/Datos/participantesNORTE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALAN.MENDOZA\Documents\Capacitacion 2026\Datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALAN.MENDOZA\Documents\GitHub\cuestionario-inpc\Capacitacion 2026\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6466B9-2889-436B-8FC1-2820014A4FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8382BFE2-6A9B-4085-B578-49AC99B3E6EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7B989F75-C598-47A3-9F2B-1AD766AC72F6}"/>
   </bookViews>
@@ -2362,9 +2362,6 @@
     <t>Alan Mendoza Hernández</t>
   </si>
   <si>
-    <t>VERONICA.AVINA</t>
-  </si>
-  <si>
     <t>S</t>
   </si>
   <si>
@@ -2372,6 +2369,9 @@
   </si>
   <si>
     <t>Veronica Avila De La Rosa</t>
+  </si>
+  <si>
+    <t>VERONICA.AVILA</t>
   </si>
 </sst>
 </file>
@@ -6417,13 +6417,13 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
+        <v>775</v>
+      </c>
+      <c r="B183" t="s">
+        <v>774</v>
+      </c>
+      <c r="C183" s="1" t="s">
         <v>772</v>
-      </c>
-      <c r="B183" t="s">
-        <v>775</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>773</v>
       </c>
       <c r="D183" s="1" t="s">
         <v>336</v>
@@ -6432,7 +6432,7 @@
         <v>279</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
